--- a/public/templates/examples/A-005-RACIMatrixForCybersecurity-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-005-RACIMatrixForCybersecurity-EXAMPLE-S.xlsx
@@ -4,11 +4,10 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -660,7 +659,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Authority</t>
@@ -692,7 +691,7 @@
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
     </row>
-    <row r="5">
+    <row r="5" ht="34.7" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Version / Dates</t>
@@ -731,7 +730,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>This matrix maps each cybersecurity function at Hickory County 911 to the roles that carry it. With a small team, the Director is accountable for most functions, county IT does much of the technical work, and the annual audit is contracted for independence.</t>
@@ -745,14 +744,14 @@
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Each row is a security function; each column is a role. R = Responsible (does the work); A = Accountable (owns the outcome, one per row); C = Consulted (gives input); I = Informed (kept up to date).</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>At Hickory County 911 the Director is both coordinator and privacy lead, so one person holds the accountable role on most rows. The contracted reviewer provides the independence the audit row needs. Columns map to the Security Role Descriptions.</t>
@@ -766,7 +765,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="34.7" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Security Function \ Role</t>
@@ -1253,7 +1252,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="66.4" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
           <t>The annual access and control review (row 14) is performed by a contracted independent reviewer, recorded in the IT Support Accountability Agreement. The CAD and ESInet vendors carry the Responsible role for configuration and backup on the systems they operate. Because the Director holds both the coordinator and privacy-lead roles, county IT gives a second view on technical risk.</t>
@@ -1302,7 +1301,7 @@
         </is>
       </c>
     </row>
-    <row r="43">
+    <row r="43" ht="34.7" customHeight="1">
       <c r="A43" s="8" t="inlineStr">
         <is>
           <t>Version</t>
@@ -1324,7 +1323,7 @@
         </is>
       </c>
     </row>
-    <row r="44">
+    <row r="44" ht="34.7" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -1373,67 +1372,8 @@
     <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>RACI Matrix: How to use</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>Rows: each is a major cybersecurity function the center performs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>Columns: each is a role. They map to the Security Role Descriptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Cells use RACI: R Responsible, A Accountable (one per row), C Consulted, I Informed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>At Hickory County 911 the Director holds the coordinator and privacy-lead roles, so the Director is Accountable on most rows.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>The annual audit is contracted to an independent reviewer for independence.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>